--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run7/epoch_50/per_file_predictions_epoch_50.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run7/epoch_50/per_file_predictions_epoch_50.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="523">
   <si>
     <t>Filename</t>
   </si>
@@ -808,772 +808,781 @@
     <t>0,1,1,0</t>
   </si>
   <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.9006,0.0212,0.0259,0.0094</t>
-  </si>
-  <si>
-    <t>0.0357,0.0029,0.0053,0.9798</t>
-  </si>
-  <si>
-    <t>0.1673,0.0240,0.0398,0.8769</t>
-  </si>
-  <si>
-    <t>0.2114,0.0032,0.0050,0.9073</t>
-  </si>
-  <si>
-    <t>0.9957,0.0016,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.9886,0.0083,0.0022,0.0006</t>
-  </si>
-  <si>
-    <t>0.9910,0.0043,0.0016,0.0006</t>
-  </si>
-  <si>
-    <t>0.9935,0.0007,0.0004,0.0016</t>
-  </si>
-  <si>
-    <t>0.9902,0.0053,0.0003,0.0010</t>
-  </si>
-  <si>
-    <t>0.9941,0.0027,0.0003,0.0005</t>
-  </si>
-  <si>
-    <t>0.9917,0.0035,0.0008,0.0009</t>
-  </si>
-  <si>
-    <t>0.9956,0.0014,0.0004,0.0004</t>
-  </si>
-  <si>
-    <t>0.2215,0.4085,0.3778,0.0089</t>
-  </si>
-  <si>
-    <t>0.4565,0.0145,0.7162,0.0031</t>
-  </si>
-  <si>
-    <t>0.1209,0.0053,0.9469,0.0005</t>
-  </si>
-  <si>
-    <t>0.1855,0.0158,0.8463,0.0006</t>
-  </si>
-  <si>
-    <t>0.7336,0.0616,0.2303,0.0052</t>
-  </si>
-  <si>
-    <t>0.0304,0.9635,0.0024,0.0006</t>
-  </si>
-  <si>
-    <t>0.0085,0.9868,0.0057,0.0005</t>
-  </si>
-  <si>
-    <t>0.7801,0.2595,0.0090,0.0057</t>
-  </si>
-  <si>
-    <t>0.5328,0.6699,0.0052,0.0025</t>
-  </si>
-  <si>
-    <t>0.0090,0.9839,0.0029,0.0003</t>
-  </si>
-  <si>
-    <t>0.5625,0.0140,0.4342,0.0452</t>
-  </si>
-  <si>
-    <t>0.2276,0.3949,0.2911,0.3163</t>
-  </si>
-  <si>
-    <t>0.0288,0.0053,0.9829,0.0005</t>
-  </si>
-  <si>
-    <t>0.1096,0.0082,0.9074,0.0042</t>
-  </si>
-  <si>
-    <t>0.3043,0.0840,0.6881,0.0101</t>
-  </si>
-  <si>
-    <t>0.0498,0.0396,0.8688,0.0414</t>
-  </si>
-  <si>
-    <t>0.0082,0.0013,0.9906,0.0009</t>
-  </si>
-  <si>
-    <t>0.8057,0.3375,0.0061,0.0025</t>
-  </si>
-  <si>
-    <t>0.6573,0.0417,0.4103,0.0094</t>
-  </si>
-  <si>
-    <t>0.0009,0.0517,0.9906,0.0024</t>
-  </si>
-  <si>
-    <t>0.0348,0.7694,0.2739,0.0021</t>
-  </si>
-  <si>
-    <t>0.7301,0.0934,0.1375,0.0756</t>
-  </si>
-  <si>
-    <t>0.8233,0.1152,0.0704,0.0061</t>
-  </si>
-  <si>
-    <t>0.5035,0.5656,0.0212,0.0099</t>
-  </si>
-  <si>
-    <t>0.0161,0.9744,0.0231,0.0025</t>
-  </si>
-  <si>
-    <t>0.1348,0.2189,0.6848,0.1207</t>
-  </si>
-  <si>
-    <t>0.0491,0.0284,0.9242,0.0170</t>
-  </si>
-  <si>
-    <t>0.0581,0.3529,0.7228,0.0186</t>
-  </si>
-  <si>
-    <t>0.2250,0.0312,0.4487,0.3228</t>
-  </si>
-  <si>
-    <t>0.0397,0.2571,0.9056,0.0086</t>
-  </si>
-  <si>
-    <t>0.0065,0.9541,0.0844,0.0006</t>
-  </si>
-  <si>
-    <t>0.0124,0.0520,0.9776,0.0013</t>
-  </si>
-  <si>
-    <t>0.0383,0.7069,0.0361,0.7045</t>
-  </si>
-  <si>
-    <t>0.0192,0.9430,0.0457,0.0370</t>
-  </si>
-  <si>
-    <t>0.0005,0.9945,0.0494,0.0002</t>
-  </si>
-  <si>
-    <t>0.0060,0.9778,0.0241,0.0132</t>
-  </si>
-  <si>
-    <t>0.0026,0.4766,0.9670,0.0022</t>
-  </si>
-  <si>
-    <t>0.0012,0.0269,0.9915,0.0017</t>
-  </si>
-  <si>
-    <t>0.0350,0.0317,0.9207,0.0134</t>
-  </si>
-  <si>
-    <t>0.0122,0.0037,0.9785,0.0034</t>
-  </si>
-  <si>
-    <t>0.0028,0.0195,0.9921,0.0006</t>
-  </si>
-  <si>
-    <t>0.0096,0.0124,0.9839,0.0015</t>
-  </si>
-  <si>
-    <t>0.9354,0.0990,0.0048,0.0007</t>
-  </si>
-  <si>
-    <t>0.9712,0.0099,0.0039,0.0047</t>
-  </si>
-  <si>
-    <t>0.9794,0.0100,0.0033,0.0023</t>
-  </si>
-  <si>
-    <t>0.0038,0.0316,0.9875,0.0008</t>
-  </si>
-  <si>
-    <t>0.9781,0.0185,0.0045,0.0009</t>
-  </si>
-  <si>
-    <t>0.9950,0.0041,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.8938,0.1683,0.0045,0.0007</t>
-  </si>
-  <si>
-    <t>0.0035,0.6580,0.9452,0.0029</t>
-  </si>
-  <si>
-    <t>0.0111,0.1580,0.9679,0.0017</t>
-  </si>
-  <si>
-    <t>0.0084,0.0058,0.9860,0.0014</t>
-  </si>
-  <si>
-    <t>0.0005,0.9472,0.9391,0.0001</t>
-  </si>
-  <si>
-    <t>0.0008,0.0129,0.9894,0.0036</t>
-  </si>
-  <si>
-    <t>0.0165,0.7351,0.4011,0.0006</t>
-  </si>
-  <si>
-    <t>0.0146,0.9772,0.0019,0.0001</t>
-  </si>
-  <si>
-    <t>0.8499,0.0226,0.2028,0.0003</t>
-  </si>
-  <si>
-    <t>0.8936,0.0367,0.0325,0.0075</t>
-  </si>
-  <si>
-    <t>0.0138,0.0969,0.9653,0.0003</t>
-  </si>
-  <si>
-    <t>0.0003,0.8981,0.9722,0.0001</t>
-  </si>
-  <si>
-    <t>0.0010,0.8575,0.8003,0.0001</t>
-  </si>
-  <si>
-    <t>0.0014,0.9574,0.2877,0.0000</t>
-  </si>
-  <si>
-    <t>0.0015,0.8754,0.8909,0.0003</t>
-  </si>
-  <si>
-    <t>0.0287,0.0038,0.3298,0.8246</t>
-  </si>
-  <si>
-    <t>0.0040,0.0027,0.0008,0.9970</t>
-  </si>
-  <si>
-    <t>0.0137,0.0022,0.0017,0.9930</t>
-  </si>
-  <si>
-    <t>0.0240,0.0054,0.0062,0.9848</t>
-  </si>
-  <si>
-    <t>0.0234,0.0095,0.0213,0.9777</t>
-  </si>
-  <si>
-    <t>0.0111,0.0007,0.0028,0.9933</t>
-  </si>
-  <si>
-    <t>0.0002,0.8806,0.9688,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.6219,0.9835,0.0002</t>
-  </si>
-  <si>
-    <t>0.0145,0.7622,0.3598,0.0018</t>
-  </si>
-  <si>
-    <t>0.0083,0.2600,0.9527,0.0026</t>
-  </si>
-  <si>
-    <t>0.0055,0.9050,0.4055,0.0002</t>
-  </si>
-  <si>
-    <t>0.0018,0.7485,0.9309,0.0005</t>
-  </si>
-  <si>
-    <t>0.9791,0.0094,0.0034,0.0026</t>
-  </si>
-  <si>
-    <t>0.9828,0.0198,0.0016,0.0004</t>
-  </si>
-  <si>
-    <t>0.9699,0.0350,0.0040,0.0008</t>
-  </si>
-  <si>
-    <t>0.9899,0.0022,0.0002,0.0018</t>
-  </si>
-  <si>
-    <t>0.9779,0.0263,0.0019,0.0005</t>
-  </si>
-  <si>
-    <t>0.9924,0.0011,0.0003,0.0020</t>
-  </si>
-  <si>
-    <t>0.9764,0.0517,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.9884,0.0059,0.0011,0.0009</t>
-  </si>
-  <si>
-    <t>0.9956,0.0014,0.0002,0.0005</t>
-  </si>
-  <si>
-    <t>0.9950,0.0027,0.0015,0.0002</t>
-  </si>
-  <si>
-    <t>0.9974,0.0015,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9954,0.0004,0.0000,0.0014</t>
-  </si>
-  <si>
-    <t>0.9889,0.0110,0.0019,0.0003</t>
-  </si>
-  <si>
-    <t>0.9892,0.0073,0.0021,0.0004</t>
-  </si>
-  <si>
-    <t>0.9924,0.0075,0.0010,0.0003</t>
-  </si>
-  <si>
-    <t>0.9929,0.0026,0.0012,0.0006</t>
-  </si>
-  <si>
-    <t>0.0037,0.0020,0.9923,0.0011</t>
-  </si>
-  <si>
-    <t>0.1311,0.0520,0.7763,0.0093</t>
-  </si>
-  <si>
-    <t>0.5650,0.0549,0.3315,0.0988</t>
-  </si>
-  <si>
-    <t>0.1220,0.0266,0.8484,0.0082</t>
-  </si>
-  <si>
-    <t>0.0276,0.9661,0.0020,0.0004</t>
-  </si>
-  <si>
-    <t>0.0589,0.9345,0.0052,0.0009</t>
-  </si>
-  <si>
-    <t>0.0361,0.9464,0.0009,0.0051</t>
-  </si>
-  <si>
-    <t>0.3591,0.7428,0.0017,0.0019</t>
-  </si>
-  <si>
-    <t>0.0502,0.9437,0.0038,0.0021</t>
-  </si>
-  <si>
-    <t>0.0201,0.9750,0.0016,0.0001</t>
-  </si>
-  <si>
-    <t>0.7015,0.4381,0.0081,0.0008</t>
-  </si>
-  <si>
-    <t>0.7017,0.0222,0.4202,0.0044</t>
-  </si>
-  <si>
-    <t>0.2181,0.0229,0.8161,0.0101</t>
-  </si>
-  <si>
-    <t>0.4853,0.1360,0.3570,0.1319</t>
-  </si>
-  <si>
-    <t>0.4375,0.0937,0.5163,0.0363</t>
-  </si>
-  <si>
-    <t>0.1258,0.1306,0.1728,0.8079</t>
-  </si>
-  <si>
-    <t>0.0054,0.9746,0.0893,0.0021</t>
-  </si>
-  <si>
-    <t>0.0003,0.9935,0.0391,0.0033</t>
-  </si>
-  <si>
-    <t>0.0520,0.9007,0.0237,0.0634</t>
-  </si>
-  <si>
-    <t>0.0002,0.9924,0.1880,0.0007</t>
-  </si>
-  <si>
-    <t>0.0110,0.9776,0.0311,0.0020</t>
-  </si>
-  <si>
-    <t>0.8163,0.2077,0.0302,0.0089</t>
-  </si>
-  <si>
-    <t>0.8643,0.2125,0.0051,0.0015</t>
-  </si>
-  <si>
-    <t>0.9913,0.0032,0.0025,0.0008</t>
-  </si>
-  <si>
-    <t>0.9860,0.0056,0.0015,0.0019</t>
-  </si>
-  <si>
-    <t>0.9767,0.0036,0.0095,0.0048</t>
-  </si>
-  <si>
-    <t>0.9619,0.0321,0.0066,0.0018</t>
-  </si>
-  <si>
-    <t>0.9884,0.0090,0.0039,0.0002</t>
-  </si>
-  <si>
-    <t>0.9890,0.0062,0.0008,0.0012</t>
-  </si>
-  <si>
-    <t>0.9913,0.0020,0.0013,0.0013</t>
-  </si>
-  <si>
-    <t>0.9835,0.0098,0.0063,0.0006</t>
-  </si>
-  <si>
-    <t>0.0038,0.5079,0.9361,0.0003</t>
-  </si>
-  <si>
-    <t>0.0002,0.7791,0.9717,0.0000</t>
-  </si>
-  <si>
-    <t>0.0033,0.1969,0.9567,0.0002</t>
-  </si>
-  <si>
-    <t>0.0314,0.2036,0.8531,0.0014</t>
-  </si>
-  <si>
-    <t>0.3863,0.3037,0.3015,0.1857</t>
-  </si>
-  <si>
-    <t>0.4438,0.2492,0.0186,0.2329</t>
-  </si>
-  <si>
-    <t>0.5145,0.0012,0.7459,0.0031</t>
-  </si>
-  <si>
-    <t>0.4984,0.1066,0.4270,0.0170</t>
-  </si>
-  <si>
-    <t>0.1109,0.0007,0.0040,0.9481</t>
-  </si>
-  <si>
-    <t>0.0010,0.0002,0.0022,0.9986</t>
-  </si>
-  <si>
-    <t>0.0144,0.0146,0.0052,0.9878</t>
-  </si>
-  <si>
-    <t>0.0417,0.0006,0.0035,0.9810</t>
-  </si>
-  <si>
-    <t>0.0019,0.7818,0.8803,0.0011</t>
-  </si>
-  <si>
-    <t>0.9192,0.1115,0.0079,0.0009</t>
-  </si>
-  <si>
-    <t>0.3254,0.7224,0.0040,0.0096</t>
-  </si>
-  <si>
-    <t>0.9619,0.0082,0.0066,0.0115</t>
-  </si>
-  <si>
-    <t>0.8620,0.1839,0.0152,0.0012</t>
-  </si>
-  <si>
-    <t>0.9576,0.0134,0.0211,0.0029</t>
-  </si>
-  <si>
-    <t>0.7860,0.0371,0.0328,0.1158</t>
-  </si>
-  <si>
-    <t>0.9082,0.0159,0.0099,0.0448</t>
-  </si>
-  <si>
-    <t>0.0004,0.0432,0.9898,0.0099</t>
-  </si>
-  <si>
-    <t>0.7260,0.0006,0.0087,0.2263</t>
-  </si>
-  <si>
-    <t>0.8631,0.0120,0.0309,0.0659</t>
-  </si>
-  <si>
-    <t>0.6530,0.3993,0.0159,0.0084</t>
-  </si>
-  <si>
-    <t>0.6518,0.3740,0.0078,0.0192</t>
-  </si>
-  <si>
-    <t>0.8529,0.1986,0.0091,0.0021</t>
-  </si>
-  <si>
-    <t>0.6121,0.2278,0.2115,0.0316</t>
-  </si>
-  <si>
-    <t>0.6991,0.2053,0.1787,0.0081</t>
-  </si>
-  <si>
-    <t>0.8919,0.0530,0.0147,0.0170</t>
-  </si>
-  <si>
-    <t>0.9866,0.0047,0.0031,0.0016</t>
-  </si>
-  <si>
-    <t>0.9825,0.0088,0.0014,0.0018</t>
-  </si>
-  <si>
-    <t>0.9883,0.0095,0.0013,0.0005</t>
-  </si>
-  <si>
-    <t>0.9821,0.0023,0.0020,0.0066</t>
-  </si>
-  <si>
-    <t>0.9838,0.0079,0.0028,0.0013</t>
-  </si>
-  <si>
-    <t>0.9922,0.0038,0.0014,0.0004</t>
-  </si>
-  <si>
-    <t>0.9780,0.0013,0.0003,0.0141</t>
-  </si>
-  <si>
-    <t>0.9852,0.0010,0.0005,0.0060</t>
-  </si>
-  <si>
-    <t>0.6891,0.3331,0.0035,0.0175</t>
-  </si>
-  <si>
-    <t>0.8306,0.3087,0.0023,0.0004</t>
-  </si>
-  <si>
-    <t>0.6898,0.4109,0.0077,0.0040</t>
-  </si>
-  <si>
-    <t>0.3185,0.2288,0.6482,0.0242</t>
-  </si>
-  <si>
-    <t>0.9443,0.1059,0.0013,0.0003</t>
-  </si>
-  <si>
-    <t>0.7376,0.2848,0.0174,0.0120</t>
-  </si>
-  <si>
-    <t>0.9548,0.0515,0.0048,0.0013</t>
-  </si>
-  <si>
-    <t>0.9422,0.0387,0.0075,0.0047</t>
-  </si>
-  <si>
-    <t>0.0023,0.0776,0.9889,0.0003</t>
-  </si>
-  <si>
-    <t>0.9687,0.0287,0.0038,0.0014</t>
-  </si>
-  <si>
-    <t>0.0048,0.0114,0.9864,0.0020</t>
-  </si>
-  <si>
-    <t>0.0082,0.1156,0.9740,0.0020</t>
-  </si>
-  <si>
-    <t>0.0397,0.0150,0.9473,0.0078</t>
-  </si>
-  <si>
-    <t>0.0138,0.0317,0.9676,0.0056</t>
-  </si>
-  <si>
-    <t>0.0082,0.0292,0.9750,0.0007</t>
-  </si>
-  <si>
-    <t>0.0087,0.0042,0.9919,0.0002</t>
-  </si>
-  <si>
-    <t>0.0279,0.0034,0.9836,0.0005</t>
-  </si>
-  <si>
-    <t>0.3868,0.3332,0.4093,0.1316</t>
-  </si>
-  <si>
-    <t>0.0981,0.0314,0.9252,0.0024</t>
-  </si>
-  <si>
-    <t>0.6664,0.0231,0.4169,0.0100</t>
-  </si>
-  <si>
-    <t>0.5720,0.0459,0.5138,0.0043</t>
-  </si>
-  <si>
-    <t>0.1415,0.5433,0.2473,0.0031</t>
-  </si>
-  <si>
-    <t>0.4152,0.1060,0.4405,0.0044</t>
-  </si>
-  <si>
-    <t>0.4695,0.1256,0.4600,0.0435</t>
-  </si>
-  <si>
-    <t>0.4981,0.0388,0.5740,0.0095</t>
-  </si>
-  <si>
-    <t>0.9421,0.0903,0.0022,0.0007</t>
-  </si>
-  <si>
-    <t>0.8770,0.2508,0.0016,0.0004</t>
-  </si>
-  <si>
-    <t>0.8446,0.2021,0.0138,0.0035</t>
-  </si>
-  <si>
-    <t>0.9328,0.1192,0.0027,0.0006</t>
-  </si>
-  <si>
-    <t>0.5928,0.5631,0.0027,0.0010</t>
-  </si>
-  <si>
-    <t>0.6648,0.0668,0.2871,0.0462</t>
-  </si>
-  <si>
-    <t>0.6628,0.0106,0.0686,0.2513</t>
-  </si>
-  <si>
-    <t>0.7019,0.1160,0.1531,0.0235</t>
-  </si>
-  <si>
-    <t>0.1588,0.2548,0.5184,0.1041</t>
-  </si>
-  <si>
-    <t>0.7691,0.0401,0.1815,0.0156</t>
-  </si>
-  <si>
-    <t>0.0439,0.0099,0.9580,0.0053</t>
-  </si>
-  <si>
-    <t>0.0390,0.2549,0.8849,0.0145</t>
-  </si>
-  <si>
-    <t>0.0081,0.2371,0.9191,0.0119</t>
-  </si>
-  <si>
-    <t>0.0763,0.0994,0.8600,0.0342</t>
-  </si>
-  <si>
-    <t>0.0148,0.0448,0.9472,0.0101</t>
-  </si>
-  <si>
-    <t>0.9912,0.0048,0.0009,0.0007</t>
-  </si>
-  <si>
-    <t>0.9857,0.0124,0.0009,0.0006</t>
-  </si>
-  <si>
-    <t>0.9838,0.0112,0.0005,0.0010</t>
-  </si>
-  <si>
-    <t>0.9851,0.0145,0.0020,0.0003</t>
-  </si>
-  <si>
-    <t>0.9912,0.0056,0.0004,0.0005</t>
-  </si>
-  <si>
-    <t>0.9871,0.0066,0.0005,0.0014</t>
-  </si>
-  <si>
-    <t>0.9926,0.0022,0.0002,0.0011</t>
-  </si>
-  <si>
-    <t>0.9864,0.0113,0.0016,0.0007</t>
-  </si>
-  <si>
-    <t>0.0194,0.0105,0.9870,0.0003</t>
-  </si>
-  <si>
-    <t>0.2648,0.3806,0.3914,0.0036</t>
-  </si>
-  <si>
-    <t>0.7807,0.0327,0.2221,0.0081</t>
-  </si>
-  <si>
-    <t>0.0248,0.0458,0.9533,0.0024</t>
-  </si>
-  <si>
-    <t>0.0015,0.0250,0.9914,0.0004</t>
-  </si>
-  <si>
-    <t>0.0180,0.0198,0.9793,0.0006</t>
-  </si>
-  <si>
-    <t>0.0018,0.0411,0.9916,0.0010</t>
-  </si>
-  <si>
-    <t>0.0500,0.0480,0.8945,0.0089</t>
-  </si>
-  <si>
-    <t>0.0176,0.0524,0.9721,0.0029</t>
-  </si>
-  <si>
-    <t>0.0280,0.0600,0.9281,0.0116</t>
-  </si>
-  <si>
-    <t>0.1026,0.1631,0.7827,0.0187</t>
-  </si>
-  <si>
-    <t>0.7141,0.0087,0.3983,0.0083</t>
-  </si>
-  <si>
-    <t>0.7325,0.0018,0.5375,0.0013</t>
-  </si>
-  <si>
-    <t>0.7658,0.0110,0.3953,0.0029</t>
-  </si>
-  <si>
-    <t>0.9644,0.0218,0.0076,0.0035</t>
-  </si>
-  <si>
-    <t>0.9723,0.0381,0.0011,0.0005</t>
-  </si>
-  <si>
-    <t>0.9941,0.0016,0.0005,0.0006</t>
-  </si>
-  <si>
-    <t>0.9755,0.0306,0.0020,0.0006</t>
-  </si>
-  <si>
-    <t>0.9832,0.0100,0.0012,0.0020</t>
-  </si>
-  <si>
-    <t>0.9934,0.0049,0.0007,0.0003</t>
-  </si>
-  <si>
-    <t>0.9867,0.0220,0.0011,0.0001</t>
-  </si>
-  <si>
-    <t>0.9796,0.0046,0.0004,0.0049</t>
-  </si>
-  <si>
-    <t>0.0469,0.0582,0.9463,0.0002</t>
-  </si>
-  <si>
-    <t>0.0031,0.1020,0.9826,0.0021</t>
-  </si>
-  <si>
-    <t>0.0219,0.1327,0.9111,0.0067</t>
-  </si>
-  <si>
-    <t>0.0285,0.0372,0.9459,0.0060</t>
-  </si>
-  <si>
-    <t>0.0108,0.0098,0.9809,0.0019</t>
-  </si>
-  <si>
-    <t>0.0358,0.0178,0.7583,0.2566</t>
-  </si>
-  <si>
-    <t>0.0449,0.0183,0.9519,0.0036</t>
-  </si>
-  <si>
-    <t>0.0241,0.0568,0.9046,0.0586</t>
-  </si>
-  <si>
-    <t>0.8879,0.0032,0.0046,0.0915</t>
-  </si>
-  <si>
-    <t>0.0571,0.2931,0.0111,0.9062</t>
-  </si>
-  <si>
-    <t>0.0363,0.0024,0.0011,0.9870</t>
-  </si>
-  <si>
-    <t>0.0150,0.0013,0.0021,0.9925</t>
-  </si>
-  <si>
-    <t>0.0048,0.0008,0.0012,0.9966</t>
-  </si>
-  <si>
-    <t>0.8244,0.0450,0.0448,0.0317</t>
+    <t>0.4325,0.2872,0.0046,0.1457</t>
+  </si>
+  <si>
+    <t>0.0743,0.0155,0.0018,0.9676</t>
+  </si>
+  <si>
+    <t>0.7557,0.0500,0.0099,0.1728</t>
+  </si>
+  <si>
+    <t>0.0308,0.0053,0.0061,0.9824</t>
+  </si>
+  <si>
+    <t>0.9954,0.0010,0.0003,0.0008</t>
+  </si>
+  <si>
+    <t>0.9960,0.0032,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9787,0.0065,0.0020,0.0035</t>
+  </si>
+  <si>
+    <t>0.9927,0.0029,0.0023,0.0006</t>
+  </si>
+  <si>
+    <t>0.9813,0.0238,0.0029,0.0003</t>
+  </si>
+  <si>
+    <t>0.9949,0.0041,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9965,0.0012,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9951,0.0003,0.0000,0.0017</t>
+  </si>
+  <si>
+    <t>0.5738,0.0443,0.5171,0.0094</t>
+  </si>
+  <si>
+    <t>0.2628,0.0501,0.7530,0.0050</t>
+  </si>
+  <si>
+    <t>0.3599,0.0104,0.7826,0.0001</t>
+  </si>
+  <si>
+    <t>0.5531,0.0119,0.6408,0.0017</t>
+  </si>
+  <si>
+    <t>0.6253,0.0873,0.4184,0.0170</t>
+  </si>
+  <si>
+    <t>0.0065,0.9900,0.0012,0.0002</t>
+  </si>
+  <si>
+    <t>0.0319,0.9701,0.0048,0.0003</t>
+  </si>
+  <si>
+    <t>0.5040,0.5952,0.0255,0.0086</t>
+  </si>
+  <si>
+    <t>0.1360,0.9053,0.0020,0.0007</t>
+  </si>
+  <si>
+    <t>0.0724,0.9557,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.6246,0.0232,0.4627,0.0056</t>
+  </si>
+  <si>
+    <t>0.3613,0.0230,0.7086,0.0165</t>
+  </si>
+  <si>
+    <t>0.0464,0.0108,0.9661,0.0025</t>
+  </si>
+  <si>
+    <t>0.1701,0.0110,0.8881,0.0027</t>
+  </si>
+  <si>
+    <t>0.3251,0.0132,0.8037,0.0023</t>
+  </si>
+  <si>
+    <t>0.0540,0.0067,0.9473,0.0025</t>
+  </si>
+  <si>
+    <t>0.0016,0.0012,0.9897,0.0051</t>
+  </si>
+  <si>
+    <t>0.8157,0.3421,0.0044,0.0005</t>
+  </si>
+  <si>
+    <t>0.3270,0.6360,0.0860,0.0144</t>
+  </si>
+  <si>
+    <t>0.0035,0.0123,0.9900,0.0012</t>
+  </si>
+  <si>
+    <t>0.0029,0.8975,0.2301,0.0010</t>
+  </si>
+  <si>
+    <t>0.7116,0.0994,0.1132,0.0894</t>
+  </si>
+  <si>
+    <t>0.1776,0.0977,0.7738,0.0022</t>
+  </si>
+  <si>
+    <t>0.8367,0.1882,0.0162,0.0011</t>
+  </si>
+  <si>
+    <t>0.0088,0.9746,0.0698,0.0047</t>
+  </si>
+  <si>
+    <t>0.0577,0.0986,0.7460,0.1549</t>
+  </si>
+  <si>
+    <t>0.1064,0.0593,0.8594,0.0317</t>
+  </si>
+  <si>
+    <t>0.0174,0.1682,0.8733,0.0613</t>
+  </si>
+  <si>
+    <t>0.0838,0.0208,0.4239,0.5940</t>
+  </si>
+  <si>
+    <t>0.0040,0.3765,0.9258,0.0004</t>
+  </si>
+  <si>
+    <t>0.0062,0.9750,0.0079,0.0003</t>
+  </si>
+  <si>
+    <t>0.0463,0.1857,0.8625,0.0103</t>
+  </si>
+  <si>
+    <t>0.0147,0.7617,0.0302,0.7191</t>
+  </si>
+  <si>
+    <t>0.0028,0.9788,0.0305,0.0224</t>
+  </si>
+  <si>
+    <t>0.0007,0.9926,0.0314,0.0007</t>
+  </si>
+  <si>
+    <t>0.0008,0.9941,0.0158,0.0020</t>
+  </si>
+  <si>
+    <t>0.0012,0.0300,0.9906,0.0023</t>
+  </si>
+  <si>
+    <t>0.0017,0.2388,0.9793,0.0006</t>
+  </si>
+  <si>
+    <t>0.0414,0.0081,0.9565,0.0026</t>
+  </si>
+  <si>
+    <t>0.1897,0.0029,0.9092,0.0027</t>
+  </si>
+  <si>
+    <t>0.0223,0.0035,0.9841,0.0008</t>
+  </si>
+  <si>
+    <t>0.0156,0.0343,0.9710,0.0013</t>
+  </si>
+  <si>
+    <t>0.9495,0.0254,0.0032,0.0070</t>
+  </si>
+  <si>
+    <t>0.9854,0.0095,0.0067,0.0003</t>
+  </si>
+  <si>
+    <t>0.9753,0.0172,0.0026,0.0021</t>
+  </si>
+  <si>
+    <t>0.0091,0.0346,0.9761,0.0013</t>
+  </si>
+  <si>
+    <t>0.9631,0.0302,0.0040,0.0021</t>
+  </si>
+  <si>
+    <t>0.9957,0.0034,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.9611,0.0408,0.0075,0.0008</t>
+  </si>
+  <si>
+    <t>0.0034,0.4975,0.9686,0.0011</t>
+  </si>
+  <si>
+    <t>0.0015,0.0205,0.9815,0.0063</t>
+  </si>
+  <si>
+    <t>0.0190,0.0621,0.9295,0.0200</t>
+  </si>
+  <si>
+    <t>0.0015,0.9126,0.9241,0.0004</t>
+  </si>
+  <si>
+    <t>0.0011,0.0034,0.9955,0.0008</t>
+  </si>
+  <si>
+    <t>0.0650,0.8781,0.0354,0.0018</t>
+  </si>
+  <si>
+    <t>0.0154,0.9801,0.0009,0.0001</t>
+  </si>
+  <si>
+    <t>0.8496,0.0235,0.2082,0.0019</t>
+  </si>
+  <si>
+    <t>0.5564,0.1744,0.3679,0.0090</t>
+  </si>
+  <si>
+    <t>0.0040,0.0088,0.9898,0.0009</t>
+  </si>
+  <si>
+    <t>0.0018,0.6333,0.9399,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.9285,0.8168,0.0000</t>
+  </si>
+  <si>
+    <t>0.0023,0.9684,0.0785,0.0005</t>
+  </si>
+  <si>
+    <t>0.0002,0.7750,0.9725,0.0001</t>
+  </si>
+  <si>
+    <t>0.0649,0.0078,0.2294,0.8183</t>
+  </si>
+  <si>
+    <t>0.0253,0.0014,0.0003,0.9926</t>
+  </si>
+  <si>
+    <t>0.0044,0.0083,0.0022,0.9953</t>
+  </si>
+  <si>
+    <t>0.0572,0.0087,0.0096,0.9690</t>
+  </si>
+  <si>
+    <t>0.0512,0.0265,0.0302,0.9528</t>
+  </si>
+  <si>
+    <t>0.0290,0.0339,0.0068,0.9780</t>
+  </si>
+  <si>
+    <t>0.0015,0.9085,0.8761,0.0008</t>
+  </si>
+  <si>
+    <t>0.0019,0.5676,0.9700,0.0004</t>
+  </si>
+  <si>
+    <t>0.0201,0.3882,0.8448,0.0117</t>
+  </si>
+  <si>
+    <t>0.0070,0.3896,0.9469,0.0006</t>
+  </si>
+  <si>
+    <t>0.0009,0.9069,0.7284,0.0001</t>
+  </si>
+  <si>
+    <t>0.0017,0.9451,0.4233,0.0001</t>
+  </si>
+  <si>
+    <t>0.9764,0.0190,0.0094,0.0003</t>
+  </si>
+  <si>
+    <t>0.9601,0.0483,0.0016,0.0010</t>
+  </si>
+  <si>
+    <t>0.9823,0.0141,0.0054,0.0006</t>
+  </si>
+  <si>
+    <t>0.9847,0.0095,0.0010,0.0013</t>
+  </si>
+  <si>
+    <t>0.9713,0.0245,0.0049,0.0018</t>
+  </si>
+  <si>
+    <t>0.9861,0.0094,0.0022,0.0009</t>
+  </si>
+  <si>
+    <t>0.9692,0.0321,0.0030,0.0012</t>
+  </si>
+  <si>
+    <t>0.9581,0.0536,0.0066,0.0006</t>
+  </si>
+  <si>
+    <t>0.9949,0.0022,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9938,0.0033,0.0006,0.0004</t>
+  </si>
+  <si>
+    <t>0.9950,0.0029,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9963,0.0016,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9963,0.0010,0.0000,0.0004</t>
+  </si>
+  <si>
+    <t>0.9946,0.0037,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9935,0.0018,0.0008,0.0008</t>
+  </si>
+  <si>
+    <t>0.9941,0.0015,0.0005,0.0008</t>
+  </si>
+  <si>
+    <t>0.0076,0.0064,0.9796,0.0052</t>
+  </si>
+  <si>
+    <t>0.3689,0.0227,0.7270,0.0058</t>
+  </si>
+  <si>
+    <t>0.6805,0.0038,0.3551,0.0220</t>
+  </si>
+  <si>
+    <t>0.0698,0.0031,0.9583,0.0010</t>
+  </si>
+  <si>
+    <t>0.0551,0.9194,0.0207,0.0036</t>
+  </si>
+  <si>
+    <t>0.0929,0.8990,0.0025,0.0066</t>
+  </si>
+  <si>
+    <t>0.1182,0.8558,0.0046,0.0229</t>
+  </si>
+  <si>
+    <t>0.1542,0.8711,0.0006,0.0022</t>
+  </si>
+  <si>
+    <t>0.2623,0.7725,0.0036,0.0078</t>
+  </si>
+  <si>
+    <t>0.0126,0.9778,0.0020,0.0006</t>
+  </si>
+  <si>
+    <t>0.7818,0.3847,0.0039,0.0010</t>
+  </si>
+  <si>
+    <t>0.3985,0.4750,0.1248,0.0093</t>
+  </si>
+  <si>
+    <t>0.4985,0.0234,0.4719,0.0648</t>
+  </si>
+  <si>
+    <t>0.3592,0.4499,0.1697,0.0799</t>
+  </si>
+  <si>
+    <t>0.3339,0.0710,0.6336,0.0105</t>
+  </si>
+  <si>
+    <t>0.1195,0.1874,0.1047,0.8440</t>
+  </si>
+  <si>
+    <t>0.0024,0.9885,0.0414,0.0013</t>
+  </si>
+  <si>
+    <t>0.0007,0.9918,0.0056,0.0249</t>
+  </si>
+  <si>
+    <t>0.0649,0.9032,0.0138,0.0152</t>
+  </si>
+  <si>
+    <t>0.0017,0.9550,0.5486,0.0010</t>
+  </si>
+  <si>
+    <t>0.0156,0.9821,0.0077,0.0002</t>
+  </si>
+  <si>
+    <t>0.7461,0.2036,0.1029,0.0229</t>
+  </si>
+  <si>
+    <t>0.9006,0.0961,0.0066,0.0088</t>
+  </si>
+  <si>
+    <t>0.9822,0.0096,0.0094,0.0009</t>
+  </si>
+  <si>
+    <t>0.9818,0.0129,0.0020,0.0013</t>
+  </si>
+  <si>
+    <t>0.9671,0.0074,0.0083,0.0075</t>
+  </si>
+  <si>
+    <t>0.9639,0.0255,0.0129,0.0014</t>
+  </si>
+  <si>
+    <t>0.9915,0.0055,0.0021,0.0002</t>
+  </si>
+  <si>
+    <t>0.9902,0.0082,0.0009,0.0004</t>
+  </si>
+  <si>
+    <t>0.9722,0.0107,0.0065,0.0034</t>
+  </si>
+  <si>
+    <t>0.9911,0.0057,0.0017,0.0003</t>
+  </si>
+  <si>
+    <t>0.0013,0.8093,0.8944,0.0002</t>
+  </si>
+  <si>
+    <t>0.0042,0.6569,0.8925,0.0005</t>
+  </si>
+  <si>
+    <t>0.0065,0.0612,0.9783,0.0004</t>
+  </si>
+  <si>
+    <t>0.0054,0.4203,0.9620,0.0008</t>
+  </si>
+  <si>
+    <t>0.5718,0.0514,0.4321,0.0395</t>
+  </si>
+  <si>
+    <t>0.6530,0.1408,0.1925,0.0593</t>
+  </si>
+  <si>
+    <t>0.4592,0.0103,0.7281,0.0056</t>
+  </si>
+  <si>
+    <t>0.5160,0.1148,0.4268,0.0328</t>
+  </si>
+  <si>
+    <t>0.1505,0.0074,0.0236,0.8996</t>
+  </si>
+  <si>
+    <t>0.0020,0.0026,0.0025,0.9976</t>
+  </si>
+  <si>
+    <t>0.0038,0.0699,0.0075,0.9906</t>
+  </si>
+  <si>
+    <t>0.0045,0.0011,0.0023,0.9964</t>
+  </si>
+  <si>
+    <t>0.0023,0.8859,0.7380,0.0046</t>
+  </si>
+  <si>
+    <t>0.9730,0.0234,0.0062,0.0009</t>
+  </si>
+  <si>
+    <t>0.7172,0.2722,0.0246,0.0291</t>
+  </si>
+  <si>
+    <t>0.9659,0.0138,0.0054,0.0035</t>
+  </si>
+  <si>
+    <t>0.7710,0.2880,0.0205,0.0009</t>
+  </si>
+  <si>
+    <t>0.9570,0.0158,0.0081,0.0058</t>
+  </si>
+  <si>
+    <t>0.0810,0.0124,0.0193,0.9438</t>
+  </si>
+  <si>
+    <t>0.9380,0.0166,0.0156,0.0147</t>
+  </si>
+  <si>
+    <t>0.0006,0.4147,0.9667,0.0076</t>
+  </si>
+  <si>
+    <t>0.8958,0.0012,0.0128,0.0474</t>
+  </si>
+  <si>
+    <t>0.8778,0.0029,0.0033,0.1170</t>
+  </si>
+  <si>
+    <t>0.5965,0.4604,0.0055,0.0057</t>
+  </si>
+  <si>
+    <t>0.7622,0.1458,0.0673,0.0294</t>
+  </si>
+  <si>
+    <t>0.8102,0.1587,0.0475,0.0098</t>
+  </si>
+  <si>
+    <t>0.3255,0.5474,0.1183,0.0094</t>
+  </si>
+  <si>
+    <t>0.7920,0.1784,0.0377,0.0060</t>
+  </si>
+  <si>
+    <t>0.4637,0.5696,0.0701,0.0343</t>
+  </si>
+  <si>
+    <t>0.9944,0.0018,0.0005,0.0006</t>
+  </si>
+  <si>
+    <t>0.9736,0.0177,0.0060,0.0019</t>
+  </si>
+  <si>
+    <t>0.9872,0.0057,0.0024,0.0008</t>
+  </si>
+  <si>
+    <t>0.9784,0.0042,0.0023,0.0069</t>
+  </si>
+  <si>
+    <t>0.9686,0.0252,0.0084,0.0010</t>
+  </si>
+  <si>
+    <t>0.9708,0.0266,0.0086,0.0009</t>
+  </si>
+  <si>
+    <t>0.9875,0.0047,0.0016,0.0014</t>
+  </si>
+  <si>
+    <t>0.9868,0.0036,0.0014,0.0017</t>
+  </si>
+  <si>
+    <t>0.6471,0.4822,0.0103,0.0048</t>
+  </si>
+  <si>
+    <t>0.8587,0.2489,0.0033,0.0002</t>
+  </si>
+  <si>
+    <t>0.4029,0.7019,0.0134,0.0012</t>
+  </si>
+  <si>
+    <t>0.1134,0.0739,0.9042,0.0081</t>
+  </si>
+  <si>
+    <t>0.7870,0.3406,0.0018,0.0011</t>
+  </si>
+  <si>
+    <t>0.9189,0.0496,0.0146,0.0063</t>
+  </si>
+  <si>
+    <t>0.9707,0.0371,0.0026,0.0004</t>
+  </si>
+  <si>
+    <t>0.8674,0.1599,0.0114,0.0035</t>
+  </si>
+  <si>
+    <t>0.0015,0.0051,0.9943,0.0010</t>
+  </si>
+  <si>
+    <t>0.9595,0.0357,0.0064,0.0012</t>
+  </si>
+  <si>
+    <t>0.0019,0.0024,0.9953,0.0004</t>
+  </si>
+  <si>
+    <t>0.0002,0.1360,0.9924,0.0018</t>
+  </si>
+  <si>
+    <t>0.0557,0.0113,0.9575,0.0017</t>
+  </si>
+  <si>
+    <t>0.0072,0.1742,0.9667,0.0028</t>
+  </si>
+  <si>
+    <t>0.0151,0.0249,0.9787,0.0012</t>
+  </si>
+  <si>
+    <t>0.0049,0.0022,0.9927,0.0008</t>
+  </si>
+  <si>
+    <t>0.0061,0.0029,0.9912,0.0011</t>
+  </si>
+  <si>
+    <t>0.4374,0.0729,0.5573,0.0507</t>
+  </si>
+  <si>
+    <t>0.3607,0.0609,0.6604,0.0161</t>
+  </si>
+  <si>
+    <t>0.7246,0.0065,0.4401,0.0059</t>
+  </si>
+  <si>
+    <t>0.0614,0.8183,0.1074,0.0022</t>
+  </si>
+  <si>
+    <t>0.1744,0.0962,0.7608,0.0114</t>
+  </si>
+  <si>
+    <t>0.4071,0.3719,0.2937,0.0300</t>
+  </si>
+  <si>
+    <t>0.0371,0.8900,0.0286,0.1024</t>
+  </si>
+  <si>
+    <t>0.4430,0.0417,0.6018,0.0083</t>
+  </si>
+  <si>
+    <t>0.9177,0.1733,0.0011,0.0003</t>
+  </si>
+  <si>
+    <t>0.8419,0.2872,0.0021,0.0011</t>
+  </si>
+  <si>
+    <t>0.6612,0.4317,0.0104,0.0025</t>
+  </si>
+  <si>
+    <t>0.9515,0.0710,0.0047,0.0009</t>
+  </si>
+  <si>
+    <t>0.8234,0.2620,0.0061,0.0017</t>
+  </si>
+  <si>
+    <t>0.7334,0.0445,0.2726,0.0041</t>
+  </si>
+  <si>
+    <t>0.7872,0.0095,0.3261,0.0047</t>
+  </si>
+  <si>
+    <t>0.6561,0.0367,0.1325,0.1522</t>
+  </si>
+  <si>
+    <t>0.6774,0.0429,0.3039,0.0273</t>
+  </si>
+  <si>
+    <t>0.5629,0.0593,0.4062,0.0348</t>
+  </si>
+  <si>
+    <t>0.0665,0.1196,0.7869,0.0132</t>
+  </si>
+  <si>
+    <t>0.1006,0.1102,0.8490,0.0286</t>
+  </si>
+  <si>
+    <t>0.0126,0.1724,0.9506,0.0029</t>
+  </si>
+  <si>
+    <t>0.0155,0.0995,0.9489,0.0024</t>
+  </si>
+  <si>
+    <t>0.0503,0.0400,0.8834,0.0243</t>
+  </si>
+  <si>
+    <t>0.9799,0.0156,0.0028,0.0010</t>
+  </si>
+  <si>
+    <t>0.9734,0.0300,0.0021,0.0008</t>
+  </si>
+  <si>
+    <t>0.9828,0.0069,0.0003,0.0025</t>
+  </si>
+  <si>
+    <t>0.9815,0.0236,0.0018,0.0003</t>
+  </si>
+  <si>
+    <t>0.9786,0.0227,0.0027,0.0005</t>
+  </si>
+  <si>
+    <t>0.9943,0.0038,0.0007,0.0003</t>
+  </si>
+  <si>
+    <t>0.9784,0.0032,0.0004,0.0095</t>
+  </si>
+  <si>
+    <t>0.9805,0.0113,0.0015,0.0015</t>
+  </si>
+  <si>
+    <t>0.0332,0.0112,0.9754,0.0006</t>
+  </si>
+  <si>
+    <t>0.2823,0.2467,0.4245,0.0047</t>
+  </si>
+  <si>
+    <t>0.9270,0.0259,0.0603,0.0049</t>
+  </si>
+  <si>
+    <t>0.0124,0.0157,0.9754,0.0037</t>
+  </si>
+  <si>
+    <t>0.0011,0.0041,0.9919,0.0034</t>
+  </si>
+  <si>
+    <t>0.0110,0.0172,0.9870,0.0003</t>
+  </si>
+  <si>
+    <t>0.0139,0.0135,0.9855,0.0011</t>
+  </si>
+  <si>
+    <t>0.0579,0.0708,0.8691,0.0084</t>
+  </si>
+  <si>
+    <t>0.0090,0.0240,0.9857,0.0011</t>
+  </si>
+  <si>
+    <t>0.0235,0.0495,0.9367,0.0164</t>
+  </si>
+  <si>
+    <t>0.1300,0.0423,0.8597,0.0018</t>
+  </si>
+  <si>
+    <t>0.5693,0.0032,0.6708,0.0045</t>
+  </si>
+  <si>
+    <t>0.6028,0.0067,0.6074,0.0052</t>
+  </si>
+  <si>
+    <t>0.8538,0.0030,0.1032,0.0146</t>
+  </si>
+  <si>
+    <t>0.9663,0.0402,0.0062,0.0012</t>
+  </si>
+  <si>
+    <t>0.9851,0.0087,0.0016,0.0015</t>
+  </si>
+  <si>
+    <t>0.9939,0.0047,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9802,0.0142,0.0027,0.0011</t>
+  </si>
+  <si>
+    <t>0.9828,0.0191,0.0012,0.0005</t>
+  </si>
+  <si>
+    <t>0.9799,0.0229,0.0016,0.0005</t>
+  </si>
+  <si>
+    <t>0.9925,0.0052,0.0008,0.0003</t>
+  </si>
+  <si>
+    <t>0.9868,0.0027,0.0008,0.0029</t>
+  </si>
+  <si>
+    <t>0.0527,0.2075,0.7653,0.0036</t>
+  </si>
+  <si>
+    <t>0.0028,0.2723,0.9610,0.0020</t>
+  </si>
+  <si>
+    <t>0.0313,0.0367,0.9560,0.0015</t>
+  </si>
+  <si>
+    <t>0.1090,0.0861,0.7948,0.0222</t>
+  </si>
+  <si>
+    <t>0.0032,0.0046,0.9822,0.0120</t>
+  </si>
+  <si>
+    <t>0.0506,0.0137,0.8189,0.1238</t>
+  </si>
+  <si>
+    <t>0.1888,0.0819,0.7353,0.0342</t>
+  </si>
+  <si>
+    <t>0.0027,0.0263,0.9825,0.0062</t>
+  </si>
+  <si>
+    <t>0.8252,0.0051,0.0238,0.1259</t>
+  </si>
+  <si>
+    <t>0.0182,0.1236,0.0038,0.9750</t>
+  </si>
+  <si>
+    <t>0.0942,0.0009,0.0005,0.9769</t>
+  </si>
+  <si>
+    <t>0.0071,0.0002,0.0003,0.9974</t>
+  </si>
+  <si>
+    <t>0.0070,0.0010,0.0043,0.9939</t>
+  </si>
+  <si>
+    <t>0.6952,0.0072,0.0102,0.3081</t>
   </si>
 </sst>
 </file>
@@ -1956,10 +1965,10 @@
         <v>259</v>
       </c>
       <c r="C2" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1973,7 +1982,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,10 +1993,10 @@
         <v>259</v>
       </c>
       <c r="C4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2001,7 +2010,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2015,7 +2024,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2029,7 +2038,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2043,7 +2052,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2057,7 +2066,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2071,7 +2080,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2085,7 +2094,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2099,7 +2108,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2113,7 +2122,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2124,10 +2133,10 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2141,7 +2150,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2155,7 +2164,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2166,10 +2175,10 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2183,7 +2192,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2197,7 +2206,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2211,7 +2220,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2222,10 +2231,10 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2239,7 +2248,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2253,7 +2262,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2267,7 +2276,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2278,10 +2287,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2295,7 +2304,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2309,7 +2318,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2323,7 +2332,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2337,7 +2346,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2351,7 +2360,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2365,7 +2374,7 @@
         <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2376,10 +2385,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D32" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2393,7 +2402,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2407,7 +2416,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2421,7 +2430,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,10 +2441,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D36" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2446,10 +2455,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2463,7 +2472,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2477,7 +2486,7 @@
         <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2491,7 +2500,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2505,7 +2514,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2516,10 +2525,10 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D42" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2533,7 +2542,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2547,7 +2556,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2561,7 +2570,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2572,10 +2581,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="D46" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2589,7 +2598,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2603,7 +2612,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2617,7 +2626,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2631,7 +2640,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2645,7 +2654,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2659,7 +2668,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2673,7 +2682,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2687,7 +2696,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2701,7 +2710,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2715,7 +2724,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2729,7 +2738,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2743,7 +2752,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2757,7 +2766,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2771,7 +2780,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2785,7 +2794,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2799,7 +2808,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2810,10 +2819,10 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D63" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2827,7 +2836,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2841,7 +2850,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2855,7 +2864,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2869,7 +2878,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2883,7 +2892,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2897,7 +2906,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2911,7 +2920,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2925,7 +2934,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2939,7 +2948,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2953,7 +2962,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2967,7 +2976,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2981,7 +2990,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2995,7 +3004,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3009,7 +3018,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3023,7 +3032,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3037,7 +3046,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3051,7 +3060,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3065,7 +3074,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3079,7 +3088,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3093,7 +3102,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3107,7 +3116,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3118,10 +3127,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D85" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3135,7 +3144,7 @@
         <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3146,10 +3155,10 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,10 +3169,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D88" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3177,7 +3186,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3191,7 +3200,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3205,7 +3214,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3219,7 +3228,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3233,7 +3242,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3247,7 +3256,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3261,7 +3270,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3275,7 +3284,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3289,7 +3298,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3303,7 +3312,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3317,7 +3326,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3331,7 +3340,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3345,7 +3354,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3359,7 +3368,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3373,7 +3382,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3387,7 +3396,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3401,7 +3410,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3415,7 +3424,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3429,7 +3438,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3443,7 +3452,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3457,7 +3466,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3471,7 +3480,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3485,7 +3494,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3499,7 +3508,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3513,7 +3522,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3527,7 +3536,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3541,7 +3550,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3552,10 +3561,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D116" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3566,10 +3575,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D117" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3580,10 +3589,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D118" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3597,7 +3606,7 @@
         <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3611,7 +3620,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3625,7 +3634,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3639,7 +3648,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3653,7 +3662,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3664,10 +3673,10 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3681,7 +3690,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3695,7 +3704,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3709,7 +3718,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3723,7 +3732,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3737,7 +3746,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3751,7 +3760,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3765,7 +3774,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3779,7 +3788,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3793,7 +3802,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3807,7 +3816,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3821,7 +3830,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3835,7 +3844,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3849,7 +3858,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3863,7 +3872,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3877,7 +3886,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3891,7 +3900,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3905,7 +3914,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3919,7 +3928,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3933,7 +3942,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3947,7 +3956,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3961,7 +3970,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3975,7 +3984,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3989,7 +3998,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4003,7 +4012,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4017,7 +4026,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4028,10 +4037,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D150" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4045,7 +4054,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4059,7 +4068,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4073,7 +4082,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4084,10 +4093,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4101,7 +4110,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4115,7 +4124,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4129,7 +4138,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4143,7 +4152,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4157,7 +4166,7 @@
         <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4171,7 +4180,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4185,7 +4194,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4196,10 +4205,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4213,7 +4222,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,10 +4233,10 @@
         <v>259</v>
       </c>
       <c r="C164" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D164" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4241,7 +4250,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4255,7 +4264,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4269,7 +4278,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4283,7 +4292,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4297,7 +4306,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4311,7 +4320,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4325,7 +4334,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4339,7 +4348,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4353,7 +4362,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4367,7 +4376,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4378,10 +4387,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4395,7 +4404,7 @@
         <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4409,7 +4418,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4423,7 +4432,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4437,7 +4446,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4451,7 +4460,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4465,7 +4474,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4479,7 +4488,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4493,7 +4502,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4507,7 +4516,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4521,7 +4530,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4535,7 +4544,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4549,7 +4558,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4563,7 +4572,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4577,7 +4586,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4588,10 +4597,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4605,7 +4614,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4619,7 +4628,7 @@
         <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4630,10 +4639,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D193" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4644,10 +4653,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4658,10 +4667,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D195" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4672,10 +4681,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D196" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4689,7 +4698,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4703,7 +4712,7 @@
         <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4717,7 +4726,7 @@
         <v>259</v>
       </c>
       <c r="D199" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4731,7 +4740,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4745,7 +4754,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4756,10 +4765,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4773,7 +4782,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4787,7 +4796,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4801,7 +4810,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,10 +4821,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4829,7 +4838,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4843,7 +4852,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4857,7 +4866,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4871,7 +4880,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4885,7 +4894,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4899,7 +4908,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4913,7 +4922,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4927,7 +4936,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4941,7 +4950,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4955,7 +4964,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4969,7 +4978,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4983,7 +4992,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4997,7 +5006,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5011,7 +5020,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5025,7 +5034,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5036,10 +5045,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D222" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5053,7 +5062,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5067,7 +5076,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5081,7 +5090,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5095,7 +5104,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5109,7 +5118,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5123,7 +5132,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5137,7 +5146,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5151,7 +5160,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5165,7 +5174,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,10 +5185,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D232" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5190,10 +5199,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D233" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5207,7 +5216,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5221,7 +5230,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5235,7 +5244,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5249,7 +5258,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5263,7 +5272,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5277,7 +5286,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5291,7 +5300,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5305,7 +5314,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5319,7 +5328,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5333,7 +5342,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5347,7 +5356,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5361,7 +5370,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5375,7 +5384,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5389,7 +5398,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5403,7 +5412,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5417,7 +5426,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5431,7 +5440,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5445,7 +5454,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5459,7 +5468,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5473,7 +5482,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5487,7 +5496,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5501,7 +5510,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5515,7 +5524,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
     </row>
   </sheetData>
